--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Back_Summary.xlsx
@@ -434,17 +434,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -456,26 +451,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.8771</v>
+        <v>17.19277</v>
       </c>
       <c r="D2" t="n">
-        <v>17.16612</v>
+        <v>16.50394</v>
       </c>
       <c r="E2" t="n">
-        <v>16.96782</v>
+        <v>16.58389</v>
       </c>
       <c r="F2" t="n">
-        <v>43.45811</v>
+        <v>22.17733</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05189</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.83449</v>
+        <v>34.86863</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +477,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.08928</v>
+        <v>17.00017</v>
       </c>
       <c r="D3" t="n">
-        <v>16.92896</v>
+        <v>16.06548</v>
       </c>
       <c r="E3" t="n">
-        <v>17.39155</v>
+        <v>16.80629</v>
       </c>
       <c r="F3" t="n">
-        <v>42.84607</v>
+        <v>22.36831</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.87098</v>
+        <v>34.46115</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +499,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.07208</v>
+        <v>16.90592</v>
       </c>
       <c r="D4" t="n">
-        <v>16.97835</v>
+        <v>16.22729</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77201</v>
+        <v>16.74885</v>
       </c>
       <c r="F4" t="n">
-        <v>42.86926</v>
+        <v>22.13089</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05115</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.87734</v>
+        <v>35.32276</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +521,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.09491</v>
+        <v>16.60292</v>
       </c>
       <c r="D5" t="n">
-        <v>16.33626</v>
+        <v>16.3472</v>
       </c>
       <c r="E5" t="n">
-        <v>17.13012</v>
+        <v>16.50195</v>
       </c>
       <c r="F5" t="n">
-        <v>43.03988</v>
+        <v>21.96745</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05149</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.82481</v>
+        <v>35.13297</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +542,20 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16.89347</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.43387</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.71185</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.08021</v>
+      </c>
+      <c r="G6" t="n">
+        <v>34.75077</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +565,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.90373</v>
+        <v>17.15163</v>
       </c>
       <c r="D7" t="n">
-        <v>16.77569</v>
+        <v>16.38767</v>
       </c>
       <c r="E7" t="n">
-        <v>16.94217</v>
+        <v>16.96738</v>
       </c>
       <c r="F7" t="n">
-        <v>43.38314</v>
+        <v>22.18498</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05142</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.84062</v>
+        <v>34.9223</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +587,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.13757</v>
+        <v>16.9895</v>
       </c>
       <c r="D8" t="n">
-        <v>16.73589</v>
+        <v>15.95173</v>
       </c>
       <c r="E8" t="n">
-        <v>16.82084</v>
+        <v>16.59543</v>
       </c>
       <c r="F8" t="n">
-        <v>43.62335</v>
+        <v>22.18347</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05196</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.84812</v>
+        <v>34.96044</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +609,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.99252</v>
+        <v>17.00149</v>
       </c>
       <c r="D9" t="n">
-        <v>17.29888</v>
+        <v>16.23488</v>
       </c>
       <c r="E9" t="n">
-        <v>16.61102</v>
+        <v>16.75302</v>
       </c>
       <c r="F9" t="n">
-        <v>43.93569</v>
+        <v>22.47427</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05095</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.88489</v>
+        <v>34.87136</v>
       </c>
     </row>
     <row r="10">
@@ -647,22 +631,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.37269</v>
+        <v>17.03946</v>
       </c>
       <c r="D10" t="n">
-        <v>17.01173</v>
+        <v>16.40254</v>
       </c>
       <c r="E10" t="n">
-        <v>17.33501</v>
+        <v>16.74461</v>
       </c>
       <c r="F10" t="n">
-        <v>43.71661</v>
+        <v>22.17941</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05071</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.88847</v>
+        <v>35.3066</v>
       </c>
     </row>
     <row r="11">
@@ -683,12 +664,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -700,23 +686,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.31351</v>
+        <v>17.53606</v>
       </c>
       <c r="D12" t="n">
-        <v>16.39309</v>
+        <v>17.09095</v>
       </c>
       <c r="E12" t="n">
-        <v>16.66029</v>
+        <v>17.10388</v>
       </c>
       <c r="F12" t="n">
-        <v>22.21195</v>
+        <v>44.22038</v>
       </c>
       <c r="G12" t="n">
-        <v>34.67341</v>
+        <v>0.05176</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.86735</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +715,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.95726</v>
+        <v>17.00335</v>
       </c>
       <c r="D13" t="n">
-        <v>16.48445</v>
+        <v>16.83627</v>
       </c>
       <c r="E13" t="n">
-        <v>16.82988</v>
+        <v>16.98167</v>
       </c>
       <c r="F13" t="n">
-        <v>22.15416</v>
+        <v>42.84506</v>
       </c>
       <c r="G13" t="n">
-        <v>34.73716</v>
+        <v>0.05198</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.87193</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +739,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>16.7133</v>
+        <v>17.03108</v>
       </c>
       <c r="D14" t="n">
-        <v>16.18111</v>
+        <v>16.59889</v>
       </c>
       <c r="E14" t="n">
-        <v>16.79793</v>
+        <v>16.95446</v>
       </c>
       <c r="F14" t="n">
-        <v>21.79223</v>
+        <v>42.81667</v>
       </c>
       <c r="G14" t="n">
-        <v>34.29428</v>
+        <v>0.0515</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.83682</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +765,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.83669</v>
+        <v>17.25356</v>
       </c>
       <c r="D15" t="n">
-        <v>16.40063</v>
+        <v>16.90081</v>
       </c>
       <c r="E15" t="n">
-        <v>16.43009</v>
+        <v>17.05215</v>
       </c>
       <c r="F15" t="n">
-        <v>22.35985</v>
+        <v>42.65561</v>
       </c>
       <c r="G15" t="n">
-        <v>34.63845</v>
+        <v>0.05085</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.85515</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +790,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.08491</v>
+        <v>17.0341</v>
       </c>
       <c r="D16" t="n">
-        <v>16.12942</v>
+        <v>16.57697</v>
       </c>
       <c r="E16" t="n">
-        <v>16.86235</v>
+        <v>16.99908</v>
       </c>
       <c r="F16" t="n">
-        <v>22.45361</v>
+        <v>43.62713</v>
       </c>
       <c r="G16" t="n">
-        <v>35.51631</v>
+        <v>0.05242</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.86522</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +815,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.97908</v>
+        <v>17.15824</v>
       </c>
       <c r="D17" t="n">
-        <v>15.94509</v>
+        <v>16.85749</v>
       </c>
       <c r="E17" t="n">
-        <v>16.9847</v>
+        <v>16.86304</v>
       </c>
       <c r="F17" t="n">
-        <v>21.79343</v>
+        <v>42.67693</v>
       </c>
       <c r="G17" t="n">
-        <v>34.87908</v>
+        <v>0.05253</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83721</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +840,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.21245</v>
+        <v>17.10774</v>
       </c>
       <c r="D18" t="n">
-        <v>15.95282</v>
+        <v>16.84797</v>
       </c>
       <c r="E18" t="n">
-        <v>16.71895</v>
+        <v>16.86376</v>
       </c>
       <c r="F18" t="n">
-        <v>21.87759</v>
+        <v>41.88544</v>
       </c>
       <c r="G18" t="n">
-        <v>34.6335</v>
+        <v>0.0525</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.8743</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +865,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.12822</v>
+        <v>17.20183</v>
       </c>
       <c r="D19" t="n">
-        <v>16.6582</v>
+        <v>16.89486</v>
       </c>
       <c r="E19" t="n">
-        <v>16.7981</v>
+        <v>17.16931</v>
       </c>
       <c r="F19" t="n">
-        <v>22.09666</v>
+        <v>43.65995</v>
       </c>
       <c r="G19" t="n">
-        <v>35.40032</v>
+        <v>0.05036</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.84327</v>
       </c>
     </row>
     <row r="20">
@@ -885,19 +890,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.91464</v>
+        <v>17.19902</v>
       </c>
       <c r="D20" t="n">
-        <v>16.1035</v>
+        <v>16.50041</v>
       </c>
       <c r="E20" t="n">
-        <v>16.88098</v>
+        <v>17.10561</v>
       </c>
       <c r="F20" t="n">
-        <v>22.29381</v>
+        <v>43.13059</v>
       </c>
       <c r="G20" t="n">
-        <v>35.65597</v>
+        <v>0.05045</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.85493</v>
       </c>
     </row>
   </sheetData>
